--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484829_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484829_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.363</v>
+        <v>6.9158</v>
       </c>
       <c r="E2" t="n">
-        <v>5.947</v>
+        <v>4.4468</v>
       </c>
       <c r="F2" t="n">
-        <v>2.416</v>
+        <v>2.469</v>
       </c>
       <c r="G2" t="n">
         <v>2.5749</v>
@@ -610,13 +610,13 @@
         <v>3.5853</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4107</v>
+        <v>0.9635</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3101</v>
+        <v>0.8099</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1006</v>
+        <v>0.1535</v>
       </c>
       <c r="V2" t="n">
         <v>1.8678</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8228</v>
+        <v>5.0298</v>
       </c>
       <c r="E3" t="n">
-        <v>2.051</v>
+        <v>3.2027</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7718</v>
+        <v>1.8272</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0649</v>
+        <v>1.0198</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4652</v>
+        <v>-3.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4003</v>
+        <v>4.0954</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0228</v>
+        <v>2.1425</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8172</v>
+        <v>-2.4073</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2057</v>
+        <v>4.5499</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0421</v>
+        <v>-1.1227</v>
       </c>
       <c r="N3" t="n">
-        <v>0.648</v>
+        <v>-0.6683</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6059</v>
+        <v>-0.4544</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.6418</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R3" t="n">
-        <v>1.887</v>
+        <v>2.8305</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4937</v>
+        <v>0.4438</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2926</v>
+        <v>0.3244</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2011</v>
+        <v>0.1194</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2642</v>
+        <v>0.9244</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6226</v>
+        <v>0.9244</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0799</v>
+        <v>4.6308</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3056</v>
+        <v>2.1483</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7742</v>
+        <v>2.4825</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0198</v>
+        <v>2.7156</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.0756</v>
+        <v>0.1902</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0954</v>
+        <v>2.5254</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1425</v>
+        <v>3.0848</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.4073</v>
+        <v>-0.7177</v>
       </c>
       <c r="L4" t="n">
-        <v>4.5499</v>
+        <v>3.8025</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1227</v>
+        <v>-0.3692</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6683</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4544</v>
+        <v>-1.277</v>
       </c>
       <c r="P4" t="n">
+        <v>1.5096</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.1322</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.6418</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.1887</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.8305</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.5062</v>
+        <v>0.4246</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5726</v>
+        <v>0.2146</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0665</v>
+        <v>0.2099</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9244</v>
+        <v>-0.019</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9244</v>
+        <v>-0.019</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0499</v>
+        <v>4.3888</v>
       </c>
       <c r="E5" t="n">
-        <v>3.082</v>
+        <v>3.3944</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9679</v>
+        <v>0.9944</v>
       </c>
       <c r="G5" t="n">
         <v>2.4144</v>
@@ -844,13 +844,13 @@
         <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1258</v>
+        <v>0.4647</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1829</v>
+        <v>0.1295</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3087</v>
+        <v>0.3351</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9434</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8576</v>
+        <v>3.9253</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3486</v>
+        <v>1.2329</v>
       </c>
       <c r="F6" t="n">
-        <v>2.509</v>
+        <v>2.6924</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7156</v>
+        <v>2.0649</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1902</v>
+        <v>2.4652</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5254</v>
+        <v>-0.4003</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0848</v>
+        <v>2.0228</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7177</v>
+        <v>1.8172</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8025</v>
+        <v>0.2057</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3692</v>
+        <v>0.0421</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.648</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.277</v>
+        <v>-0.6059</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6418</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3486</v>
+        <v>0.5962</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.585</v>
+        <v>0.4745</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2364</v>
+        <v>0.1218</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.019</v>
+        <v>1.2642</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.019</v>
+        <v>0.6226</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7686</v>
+        <v>2.7127</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0111</v>
+        <v>0.8494</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7575</v>
+        <v>1.8633</v>
       </c>
       <c r="G8" t="n">
         <v>1.019</v>
@@ -1078,13 +1078,13 @@
         <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6843</v>
+        <v>0.2598</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7519</v>
+        <v>0.0864</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1735</v>
       </c>
       <c r="V8" t="n">
         <v>1.2452</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.3349</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.191</v>
+        <v>0.0095</v>
       </c>
       <c r="F9" t="n">
-        <v>1.895</v>
+        <v>0.3254</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6291</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.486</v>
+        <v>0.0697</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1431</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8535</v>
+        <v>0.0296</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1166</v>
+        <v>0.0211</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9701</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7756</v>
+        <v>0.0485</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6026</v>
+        <v>0.0485</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.173</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0499</v>
+        <v>0.068</v>
       </c>
       <c r="T9" t="n">
-        <v>0.606</v>
+        <v>-0.0201</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4439</v>
+        <v>0.0882</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1258</v>
+        <v>0.2203</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1467</v>
+        <v>-1.4631</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2725</v>
+        <v>1.6834</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07820000000000001</v>
+        <v>-1.6291</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0697</v>
+        <v>-0.486</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008500000000000001</v>
+        <v>-1.1431</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0296</v>
+        <v>-0.8535</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0211</v>
+        <v>0.1166</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.9701</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0485</v>
+        <v>-0.7756</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0485</v>
+        <v>-0.6026</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.173</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1411</v>
+        <v>0.5661</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1764</v>
+        <v>0.3338</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0353</v>
+        <v>0.2323</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5977</v>
+        <v>0.1167</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5459</v>
+        <v>-1.8051</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9483</v>
+        <v>1.9218</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1404</v>
@@ -1312,13 +1312,13 @@
         <v>2.2644</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7971</v>
+        <v>-0.0827</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6808</v>
+        <v>0.0601</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1163</v>
+        <v>-0.1428</v>
       </c>
       <c r="V11" t="n">
         <v>0.019</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2395</v>
+        <v>-1.5562</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3335</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.906</v>
+        <v>-0.8531</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1081</v>
@@ -1390,13 +1390,13 @@
         <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9817</v>
+        <v>0.665</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9123</v>
+        <v>0.5427</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0694</v>
+        <v>0.1223</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2452</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4447</v>
+        <v>-3.3473</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6187</v>
+        <v>-1.5213</v>
       </c>
       <c r="F13" t="n">
         <v>-1.826</v>
@@ -1468,10 +1468,10 @@
         <v>0.3774</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5073</v>
+        <v>-0.4099</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U13" t="n">
         <v>-0.0958</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.9085</v>
+        <v>26.7903</v>
       </c>
       <c r="E14" t="n">
-        <v>12.3282</v>
+        <v>13.2101</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5802</v>
+        <v>13.5803</v>
       </c>
       <c r="G14" t="n">
-        <v>8.3583</v>
+        <v>8.358300000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4068999999999998</v>
+        <v>-0.4069000000000003</v>
       </c>
       <c r="I14" t="n">
         <v>8.765000000000001</v>
@@ -1522,13 +1522,13 @@
         <v>14.4378</v>
       </c>
       <c r="K14" t="n">
-        <v>3.184999999999999</v>
+        <v>3.185</v>
       </c>
       <c r="L14" t="n">
         <v>11.2529</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.079700000000001</v>
+        <v>-6.0797</v>
       </c>
       <c r="N14" t="n">
         <v>-3.592</v>
@@ -1546,16 +1546,16 @@
         <v>21.70050000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0772</v>
+        <v>3.9591</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759899999999999</v>
+        <v>2.6417</v>
       </c>
       <c r="U14" t="n">
         <v>1.3174</v>
       </c>
       <c r="V14" t="n">
-        <v>2.207599999999999</v>
+        <v>2.2076</v>
       </c>
       <c r="W14" t="n">
         <v>5.5654</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4239</v>
+        <v>-0.371</v>
       </c>
       <c r="E16" t="n">
         <v>-0.0964</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3275</v>
+        <v>-0.2746</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2117</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2122</v>
+        <v>-0.1593</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.5264</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0522</v>
+        <v>0.8375</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8093</v>
+        <v>-1.3639</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8495</v>
+        <v>0.1875</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1113</v>
+        <v>0.1268</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2618</v>
+        <v>0.0607</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0554</v>
+        <v>1.2003</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0142</v>
+        <v>0.5337</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0411</v>
+        <v>0.6666</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2059</v>
+        <v>-1.0128</v>
       </c>
       <c r="N17" t="n">
-        <v>0.097</v>
+        <v>-0.4069</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.303</v>
+        <v>-0.6059</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4779</v>
+        <v>0.0974</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7795</v>
+        <v>-0.0419</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3016</v>
+        <v>0.1394</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1194</v>
+        <v>-0.8591</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3503</v>
+        <v>-0.4419</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4697</v>
+        <v>-0.4172</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1875</v>
+        <v>0.8495</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1268</v>
+        <v>1.1113</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0607</v>
+        <v>-0.2618</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2003</v>
+        <v>1.0554</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5337</v>
+        <v>1.0142</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6666</v>
+        <v>0.0411</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0128</v>
+        <v>-0.2059</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4069</v>
+        <v>0.097</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6059</v>
+        <v>-0.303</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4956</v>
+        <v>0.4803</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5291</v>
+        <v>0.3897</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0335</v>
+        <v>0.0905</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4258</v>
+        <v>-1.5347</v>
       </c>
       <c r="E19" t="n">
-        <v>1.664</v>
+        <v>-1.9999</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0898</v>
+        <v>0.4652</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5291</v>
+        <v>-1.0585</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2739</v>
+        <v>1.0737</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.803</v>
+        <v>-2.1322</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3548</v>
+        <v>0.3893</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7294</v>
+        <v>1.548</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6254999999999999</v>
+        <v>-1.1587</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.884</v>
+        <v>-1.4478</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4555</v>
+        <v>-0.4742</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4285</v>
+        <v>-0.9735</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3486</v>
+        <v>0.1014</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3092</v>
+        <v>-0.483</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0394</v>
+        <v>0.5844</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2452</v>
+        <v>1.3094</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-0.5584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8724</v>
+        <v>-1.5617</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2127</v>
+        <v>1.3717</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6597</v>
+        <v>-2.9334</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8164</v>
+        <v>-0.5291</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0808</v>
+        <v>0.2739</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2643</v>
+        <v>-0.803</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1808</v>
+        <v>1.3548</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5596</v>
+        <v>0.7294</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7403</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9972</v>
+        <v>-1.884</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5212</v>
+        <v>-0.4555</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.476</v>
+        <v>-1.4285</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3404</v>
+        <v>0.2126</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1916</v>
+        <v>0.0169</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1488</v>
+        <v>0.1958</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2969</v>
+        <v>-2.0046</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4874</v>
+        <v>-0.5848</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8095</v>
+        <v>-1.4198</v>
       </c>
       <c r="G21" t="n">
         <v>2.9068</v>
@@ -2092,13 +2092,13 @@
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2228</v>
+        <v>0.5151</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0653</v>
+        <v>-0.1628</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2881</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4073</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4491</v>
+        <v>-2.0151</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5845</v>
+        <v>-1.3152</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1355</v>
+        <v>-0.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0585</v>
+        <v>-0.8466</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0737</v>
+        <v>1.3719</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1322</v>
+        <v>-2.2185</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3893</v>
+        <v>1.3208</v>
       </c>
       <c r="K22" t="n">
-        <v>1.548</v>
+        <v>1.7647</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1587</v>
+        <v>-0.4439</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4478</v>
+        <v>-2.1674</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4742</v>
+        <v>-0.3928</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9735</v>
+        <v>-1.7746</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.5661</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.887</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.774</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8129</v>
+        <v>-0.6666</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0676</v>
+        <v>-0.749</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2547</v>
+        <v>0.0824</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3094</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5584</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9184</v>
+        <v>-2.1125</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4026</v>
+        <v>-2.0129</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5158</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3725</v>
@@ -2248,13 +2248,13 @@
         <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0928</v>
+        <v>-0.2869</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7519</v>
+        <v>-0.3622</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3409</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>1.8678</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2097</v>
+        <v>-2.1694</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6307</v>
+        <v>-1.505</v>
       </c>
       <c r="F24" t="n">
-        <v>0.421</v>
+        <v>-0.6644</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2942</v>
+        <v>-0.8164</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5823</v>
+        <v>-1.0808</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7119</v>
+        <v>0.2643</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7181</v>
+        <v>0.1808</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7592</v>
+        <v>-0.5596</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0411</v>
+        <v>0.7403</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5761</v>
+        <v>-0.9972</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1769</v>
+        <v>-0.5212</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.753</v>
+        <v>-0.476</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0757</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7942</v>
+        <v>0.0434</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5596</v>
+        <v>-0.1007</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2347</v>
+        <v>0.1441</v>
       </c>
       <c r="V24" t="n">
-        <v>0.366</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5547</v>
+        <v>-3.4478</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7049</v>
+        <v>-4.0204</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8498</v>
+        <v>0.5726</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8466</v>
+        <v>-2.2942</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3719</v>
+        <v>-0.5823</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.2185</v>
+        <v>-1.7119</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3208</v>
+        <v>-0.7181</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7647</v>
+        <v>-0.7592</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4439</v>
+        <v>0.0411</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1674</v>
+        <v>-1.5761</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3928</v>
+        <v>0.1769</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7746</v>
+        <v>-1.753</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5661</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2062</v>
+        <v>0.5561</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1387</v>
+        <v>0.1698</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0674</v>
+        <v>0.3863</v>
       </c>
       <c r="V25" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.366</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X25" t="n">
         <v>0.06419999999999999</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.0938</v>
+        <v>-5.7258</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7401</v>
+        <v>-4.1299</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3536</v>
+        <v>-1.5959</v>
       </c>
       <c r="G26" t="n">
         <v>-4.4898</v>
@@ -2482,13 +2482,13 @@
         <v>1.3209</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4415</v>
+        <v>-0.0735</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5131</v>
+        <v>0.1234</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9546</v>
+        <v>-0.1969</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5964</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-25.9085</v>
+        <v>-22.0111</v>
       </c>
       <c r="E27" t="n">
         <v>-13.5802</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.3282</v>
+        <v>-8.430999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-8.358000000000001</v>
@@ -2533,7 +2533,7 @@
         <v>-8.7651</v>
       </c>
       <c r="J27" t="n">
-        <v>6.0797</v>
+        <v>6.079699999999999</v>
       </c>
       <c r="K27" t="n">
         <v>3.5919</v>
@@ -2560,13 +2560,13 @@
         <v>9.435</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.0773</v>
+        <v>0.82</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.3172</v>
+        <v>-1.3174</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.7599</v>
+        <v>2.1375</v>
       </c>
       <c r="V27" t="n">
         <v>-2.2075</v>
@@ -2575,7 +2575,7 @@
         <v>3.3578</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.565300000000002</v>
+        <v>-5.565300000000001</v>
       </c>
     </row>
   </sheetData>
